--- a/04_DESIGN_TABLES/DesignTable_5503.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5503.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,16 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,7 +521,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.83</v>
+        <v>0.188</v>
       </c>
       <c r="F3" t="n">
         <v>0.33</v>
@@ -539,7 +549,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Air-Way s154 only (double-pass 15 rows)</t>
+          <t>Air-Way s154 only (double-pass 15 rows) | D (male bore) 0.188 = Brennan TFA catalog p.32 (5503-FG MP-FP 45 DEG ELBOW STREET ELBOW) A1 DRILL; Air-Way plain twins agree 10/10 (wave2 tee_elbow mapping_evidence.txt l.130) - Q-ANGLED-5503D settled from Brennan 2026-10-18 (Air-Way printed a value larger than the thread; PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -685,7 +695,7 @@
         <v>0.75</v>
       </c>
       <c r="E6" t="n">
-        <v>1.19</v>
+        <v>0.281</v>
       </c>
       <c r="F6" t="n">
         <v>0.43</v>
@@ -713,7 +723,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Air-Way s154 only (double-pass 15 rows)</t>
+          <t>Air-Way s154 only (double-pass 15 rows) | D (male bore) 0.281 = Brennan TFA catalog p.32 (5503-FG MP-FP 45 DEG ELBOW STREET ELBOW) A1 DRILL; Air-Way plain twins agree 10/10 (wave2 tee_elbow mapping_evidence.txt l.130) - Q-ANGLED-5503D settled from Brennan 2026-10-18 (Air-Way printed a value larger than the thread; PROPOSAL, genfeat ANGLED) | PORTDEPTH 0.56 = Brennan port depth -04 = 0.560 on 2502-06-04-FG, 5405-04-04, 5406-08-04, 5502-04-04-FG STEPs (tools/_out/genfeat_20261018/angled/scripts/brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -725,6 +735,9 @@
         <is>
           <t>5503-04-04-FG</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -829,7 +842,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Air-Way s154 only (double-pass 15 rows)</t>
+          <t>Air-Way s154 only (double-pass 15 rows) | PORTDEPTH 0.58 = Brennan port depth -06 = 0.580 on 1504-06-06-FG, 2611-06-06-06-FG, 5601-06-06-06-FG STEPs (tools/_out/genfeat_20261018/angled/scripts/brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -841,6 +854,9 @@
         <is>
           <t>5503-06-06-FG</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="9">
@@ -917,7 +933,7 @@
         <v>1.06</v>
       </c>
       <c r="E10" t="n">
-        <v>1.54</v>
+        <v>0.531</v>
       </c>
       <c r="F10" t="n">
         <v>0.7</v>
@@ -945,7 +961,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Air-Way s154 only (double-pass 15 rows)</t>
+          <t>Air-Way s154 only (double-pass 15 rows) | D (male bore) 0.531 = Brennan TFA catalog p.32 (5503-FG MP-FP 45 DEG ELBOW STREET ELBOW) A1 DRILL; Air-Way plain twins agree 10/10 (wave2 tee_elbow mapping_evidence.txt l.130) - Q-ANGLED-5503D settled from Brennan 2026-10-18 (Air-Way printed a value larger than the thread; PROPOSAL, genfeat ANGLED) | PORTDEPTH 0.75 = Brennan port depth -08 = 0.750 on 12 Brennan -08 female-port STEPs (1502, 2505, 2606, 2705, 5405, 5502, 5504, 5505, 5603, 5605, 5652, 6420) (tools/_out/genfeat_20261018/angled/scripts/brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -957,6 +973,9 @@
         <is>
           <t>5503-08-08-FG</t>
         </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1033,7 +1052,7 @@
         <v>1.31</v>
       </c>
       <c r="E12" t="n">
-        <v>1.64</v>
+        <v>0.719</v>
       </c>
       <c r="F12" t="n">
         <v>0.91</v>
@@ -1061,7 +1080,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Air-Way s154 only (double-pass 15 rows)</t>
+          <t>Air-Way s154 only (double-pass 15 rows) | D (male bore) 0.719 = Brennan TFA catalog p.32 (5503-FG MP-FP 45 DEG ELBOW STREET ELBOW) A1 DRILL; Air-Way plain twins agree 10/10 (wave2 tee_elbow mapping_evidence.txt l.130) - Q-ANGLED-5503D settled from Brennan 2026-10-18 (Air-Way printed a value larger than the thread; PROPOSAL, genfeat ANGLED)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1556,24 +1575,50 @@
           <t>5503-16-16-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.315</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>5503-16-16-FG</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1-11 1/2 (A (1) NPTF) x 1-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-16-16 (differs by -FG suffix) -&gt; dims NOT copied | PORTDEPTH 0.94 = Brennan port depth -16 = 0.940 on the part's OWN STEP 5503-16-16-FG (and 5405-16-16, 5502-16-16-FG) (tools/_out/genfeat_20261018/angled/scripts/brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (PROPOSAL, genfeat ANGLED) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1584,6 +1629,14 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>5503-16-16-FG</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1593,24 +1646,50 @@
           <t>5503-20-20-FG</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.66</v>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>5503-20-20-FG</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 (A (1) NPTF) x 1 1/4-11 1/2 (A (2) NPTF)</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-20-20 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1621,6 +1700,11 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>5503-20-20-FG</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
